--- a/Scoring Logic and Documentation/method/entropy_weights.xlsx
+++ b/Scoring Logic and Documentation/method/entropy_weights.xlsx
@@ -478,28 +478,28 @@
         <v>0.3</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2686826806918144</v>
+        <v>0.2724233791491785</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3364509052363785</v>
+        <v>0.3373637073689004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1931820745121725</v>
+        <v>0.1904603094003465</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3353560355741635</v>
+        <v>0.3332241012030146</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03131731930818554</v>
+        <v>0.02757662085082152</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03645090523637851</v>
+        <v>0.03736370736890043</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1068179254878275</v>
+        <v>0.1095396905996535</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0353560355741635</v>
+        <v>0.03322410120301461</v>
       </c>
     </row>
     <row r="3">
@@ -512,28 +512,28 @@
         <v>0.35</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3710458202681205</v>
+        <v>0.3701337959499669</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3203795033433237</v>
+        <v>0.3148134821932385</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4651563417489527</v>
+        <v>0.4667255263970893</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3156106858187211</v>
+        <v>0.3181531880446986</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02104582026812052</v>
+        <v>0.02013379594996689</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02962049665667627</v>
+        <v>0.03518651780676152</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1151563417489527</v>
+        <v>0.1167255263970893</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03438931418127888</v>
+        <v>0.03184681195530137</v>
       </c>
     </row>
     <row r="4">
@@ -546,28 +546,28 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1614895048497469</v>
+        <v>0.171469134070057</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2694864993731558</v>
+        <v>0.2776395167198066</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1236147136516962</v>
+        <v>0.1240317225012729</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1220141294665648</v>
+        <v>0.1229970530800816</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03851049515025309</v>
+        <v>0.02853086592994297</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06948649937315576</v>
+        <v>0.07763951671980657</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07638528634830379</v>
+        <v>0.07596827749872707</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07798587053343521</v>
+        <v>0.07700294691991842</v>
       </c>
     </row>
     <row r="5">
@@ -580,28 +580,28 @@
         <v>0.15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1987819941903182</v>
+        <v>0.1859736908307976</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07368309204714199</v>
+        <v>0.07018329371805455</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2180468700871786</v>
+        <v>0.2187824417012913</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2270191491405506</v>
+        <v>0.2256256576722052</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04878199419031817</v>
+        <v>0.0359736908307976</v>
       </c>
       <c r="H5" t="n">
-        <v>0.076316907952858</v>
+        <v>0.07981670628194544</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06804687008717861</v>
+        <v>0.0687824417012913</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07701914914055064</v>
+        <v>0.07562565767220519</v>
       </c>
     </row>
   </sheetData>
